--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R2391e66c2eb743d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R4f69346034e54f68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R90695cc8a5e84d43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R08f03a76068740b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R2ac11b1a6dca40b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9e92bd9285944ca7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Ra595f541b4c84636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R4480807f1453426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R70c354687dc64098"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Re0c8f1047d294d5b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -534,7 +534,7 @@
         <x:v>billing_meta.billing_period_start</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>2026年7月1日00:00:00Z</x:v>
+        <x:v>ISO8601值2026-07-01T00:00:00Z</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>billing_contract.json的billing_period_start_utc</x:v>
@@ -548,7 +548,7 @@
         <x:v>billing_meta.billing_period_end</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>2026年8月1日00:00:00Z</x:v>
+        <x:v>ISO8601值2026-08-01T00:00:00Z</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
         <x:v>billing_contract.json的billing_period_end_utc</x:v>

--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9e92bd9285944ca7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Ra595f541b4c84636"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R4480807f1453426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R70c354687dc64098"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Re0c8f1047d294d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R4303a0ba62ab4ae9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rb3f0235820ae476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R40169e3c7c9b4dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rbe1bf5dd87ce42a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R82671ba919914707"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -425,7 +425,7 @@
         <x:v>正确值</x:v>
       </x:c>
       <x:c r="D1" s="9" t="str">
-        <x:v>来源与验证</x:v>
+        <x:v>来源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" customHeight="1">
@@ -669,7 +669,7 @@
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>reference_members</x:v>
+        <x:v>delivery_paths</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
         <x:v>output/api_billing_repaired.db,output/rebuild_api_billing.sql,output/reports/tenant_invoice.csv,output/reports/family_usage.csv,output/reports/exclusion_review.csv</x:v>
@@ -678,7 +678,7 @@
         <x:v>相对路径逐字匹配</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>reference.zip成员</x:v>
+        <x:v>交付物清单</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -940,7 +940,7 @@
         <x:v>允许范围</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
-        <x:v>不变条件</x:v>
+        <x:v>仍需满足</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" customHeight="1">
